--- a/data/UV-Vis/2_Sb2Se3_Corrected.xlsx
+++ b/data/UV-Vis/2_Sb2Se3_Corrected.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{11F76DA0-7ABC-4663-98A9-794640C993C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{10F234B2-87E0-4953-9FA4-BFC1EAD52666}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{10F234B2-87E0-4953-9FA4-BFC1EAD52666}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32474,7 +32474,7 @@
         <v>41.263489999999997</v>
       </c>
       <c r="C1282">
-        <f t="shared" ref="C1282:C1345" si="40">B1282+J1282</f>
+        <f t="shared" ref="C1282:C1302" si="40">B1282+J1282</f>
         <v>46.876509999999996</v>
       </c>
       <c r="H1282">
@@ -32484,7 +32484,7 @@
         <v>10.376720000000001</v>
       </c>
       <c r="J1282">
-        <f t="shared" ref="J1282:J1345" si="41">K1282-H1282-I1282</f>
+        <f t="shared" ref="J1282:J1302" si="41">K1282-H1282-I1282</f>
         <v>5.613019999999997</v>
       </c>
       <c r="K1282">
